--- a/education_forms/044_graduate_program_application_form--education_forms.xlsx
+++ b/education_forms/044_graduate_program_application_form--education_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>resume_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Resume</t>
+          <t>Resume 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>transcripts</t>
+          <t>transcripts_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Transcripts</t>
+          <t>Transcripts 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>personal_statement</t>
+          <t>personal_statement_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Personal Statement</t>
+          <t>Personal Statement 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>resume_attachment</t>
+          <t>resume_attachment_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Resume Attachment</t>
+          <t>Resume Attachment 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>transcripts_attachment</t>
+          <t>transcripts_attachment_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Transcripts Attachment</t>
+          <t>Transcripts Attachment 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>letters_of_recommendation_attachment</t>
+          <t>letters_of_recommendation_attachment_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Letters Of Recommendation Attachment</t>
+          <t>Letters Of Recommendation Attachment 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>personal_statement_attachment</t>
+          <t>personal_statement_attachment_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Personal Statement Attachment</t>
+          <t>Personal Statement Attachment 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
